--- a/Файлы/1 курс/2 семестр/Теоретическая информатика/Лабы/07.05.25 - Лаба №7/Дима/Лаб7.xlsx
+++ b/Файлы/1 курс/2 семестр/Теоретическая информатика/Лабы/07.05.25 - Лаба №7/Дима/Лаб7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luvidmi\Desktop\gitRep\Codespace\Файлы\1 курс\2 семестр\Теоретическая информатика\Лабы\07.05.25 - Лаба №7\Дима\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7642B3E-056F-47EE-88BB-8CA9D109564E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A654A902-295E-4771-95E7-0093407FFD88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -308,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -368,14 +368,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1780,10 +1783,10 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="1"/>
@@ -1813,7 +1816,7 @@
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23">
+      <c r="A3" s="22">
         <v>1001</v>
       </c>
       <c r="B3" s="23" t="s">
@@ -1822,27 +1825,27 @@
       <c r="D3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="24">
         <v>700</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="24">
         <v>800</v>
       </c>
-      <c r="H3" s="21">
+      <c r="H3" s="24">
         <v>68</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="24">
         <v>15</v>
       </c>
-      <c r="J3" s="21">
+      <c r="J3" s="24">
         <v>0.89</v>
       </c>
-      <c r="K3" s="21">
+      <c r="K3" s="24">
         <v>0.95</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23">
+      <c r="A4" s="22">
         <v>1002</v>
       </c>
       <c r="B4" s="23" t="s">
@@ -1851,27 +1854,27 @@
       <c r="D4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="24">
         <v>700</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="24">
         <v>800</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="24">
         <v>128</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="24">
         <v>15</v>
       </c>
-      <c r="J4" s="21">
+      <c r="J4" s="24">
         <v>0.89</v>
       </c>
-      <c r="K4" s="21">
+      <c r="K4" s="24">
         <v>0.95</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23">
+      <c r="A5" s="22">
         <v>1003</v>
       </c>
       <c r="B5" s="23" t="s">
@@ -1880,27 +1883,27 @@
       <c r="D5" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="24">
         <v>700</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="24">
         <v>800</v>
       </c>
-      <c r="H5" s="21">
+      <c r="H5" s="24">
         <v>106</v>
       </c>
-      <c r="I5" s="21">
+      <c r="I5" s="24">
         <v>15</v>
       </c>
-      <c r="J5" s="21">
+      <c r="J5" s="24">
         <v>0.89</v>
       </c>
-      <c r="K5" s="21">
+      <c r="K5" s="24">
         <v>0.95</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23">
+      <c r="A6" s="22">
         <v>1004</v>
       </c>
       <c r="B6" s="23" t="s">
@@ -1909,27 +1912,27 @@
       <c r="D6" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="24">
         <v>1000</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="24">
         <v>2300</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="24">
         <v>419</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="24">
         <v>15</v>
       </c>
-      <c r="J6" s="21">
+      <c r="J6" s="24">
         <v>0.89</v>
       </c>
-      <c r="K6" s="21">
+      <c r="K6" s="24">
         <v>0.95</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23">
+      <c r="A7" s="22">
         <v>1005</v>
       </c>
       <c r="B7" s="23" t="s">
@@ -1938,27 +1941,27 @@
       <c r="D7" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="24">
         <v>1200</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="24">
         <v>1800</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="24">
         <v>4587</v>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="24">
         <v>15</v>
       </c>
-      <c r="J7" s="21">
+      <c r="J7" s="24">
         <v>0.89</v>
       </c>
-      <c r="K7" s="21">
+      <c r="K7" s="24">
         <v>0.95</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="23">
+      <c r="A8" s="22">
         <v>1006</v>
       </c>
       <c r="B8" s="23" t="s">
@@ -1967,22 +1970,22 @@
       <c r="D8" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="24">
         <v>1000</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="24">
         <v>2300</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="24">
         <v>1057</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="24">
         <v>15</v>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="24">
         <v>0.89</v>
       </c>
-      <c r="K8" s="21">
+      <c r="K8" s="24">
         <v>0.95</v>
       </c>
     </row>
